--- a/Project 1 Data Quality Assessment/D6 Parallel-redundancy Temporal Consistency/outputs/data/D6_mapping_params.xlsx
+++ b/Project 1 Data Quality Assessment/D6 Parallel-redundancy Temporal Consistency/outputs/data/D6_mapping_params.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pair_quantiles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="public_quantiles" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="aggregation" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="deadband" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="version" sheetId="4" state="visible" r:id="rId4"/>
@@ -19,10 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,12 +58,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,61 +428,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>pair_id</t>
+          <t>mapping_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>regime_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>subscore</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>risk_metric</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>q50</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>q75</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>q90</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>q97_5</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sample_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>exact_stratum_size</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>mapping_scope</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>calibration_quality</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>benchmark_source</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>calibration_end_exclusive</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>mapping_type</t>
         </is>
@@ -495,1260 +511,1878 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PAIR_DO11</t>
+          <t>DO-R2.0-Q_dist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Q_dist</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>risk_dist</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>0.3399862762371273</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.5268839558211236</v>
-      </c>
       <c r="F2" t="n">
-        <v>0.756919124263561</v>
+        <v>0.2504154359800578</v>
       </c>
       <c r="G2" t="n">
-        <v>1.235163442312704</v>
+        <v>0.3338236766084912</v>
       </c>
       <c r="H2" t="n">
-        <v>4139</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.4280023665920573</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6602663723924389</v>
+      </c>
+      <c r="J2" t="n">
+        <v>344</v>
+      </c>
+      <c r="K2" t="n">
+        <v>344</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>variable_regime_public</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>adequate</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAIR_DO11</t>
+          <t>DO-R2.0-Q_trend</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Q_trend</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>risk_trend</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>0.681375655305887</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.254103762851769</v>
-      </c>
       <c r="F3" t="n">
-        <v>1.944594944068816</v>
+        <v>0.5367493751120398</v>
       </c>
       <c r="G3" t="n">
-        <v>2.915792990111726</v>
+        <v>0.9088822902507345</v>
       </c>
       <c r="H3" t="n">
-        <v>4139</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>1.262118579655626</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.606347933993035</v>
+      </c>
+      <c r="J3" t="n">
+        <v>344</v>
+      </c>
+      <c r="K3" t="n">
+        <v>344</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>variable_regime_public</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>adequate</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAIR_DO11</t>
+          <t>DO-R2.0-Q_var</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Q_var</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>risk_var</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>0.1213213544945876</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.3837691303577554</v>
-      </c>
       <c r="F4" t="n">
-        <v>0.6552250549992011</v>
+        <v>0.1549026540026797</v>
       </c>
       <c r="G4" t="n">
-        <v>1.017213994225128</v>
+        <v>0.2643708304244196</v>
       </c>
       <c r="H4" t="n">
-        <v>4139</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.4083907052416982</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5931410151814244</v>
+      </c>
+      <c r="J4" t="n">
+        <v>344</v>
+      </c>
+      <c r="K4" t="n">
+        <v>344</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>variable_regime_public</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>adequate</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAIR_DO11</t>
+          <t>DO-R3.0-Q_dist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Q_cp</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>risk_cp</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.234823173596727</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.4292550832035611</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>risk_dist</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>0.6552298787725418</v>
+        <v>0.4576931600782945</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9034736031450495</v>
+        <v>0.5935612000600703</v>
       </c>
       <c r="H5" t="n">
-        <v>4139</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.7789426749644821</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.073665920603763</v>
+      </c>
+      <c r="J5" t="n">
+        <v>232</v>
+      </c>
+      <c r="K5" t="n">
+        <v>232</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>variable_regime_public</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>adequate</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PAIR_DO12</t>
+          <t>DO-R3.0-Q_trend</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Q_dist</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>risk_dist</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.2704876339739005</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.4105704176961075</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>risk_trend</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>0.5977071667699472</v>
+        <v>0.9738773107279557</v>
       </c>
       <c r="G6" t="n">
-        <v>0.958983046395997</v>
+        <v>1.606268008652675</v>
       </c>
       <c r="H6" t="n">
-        <v>4231</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>2.234776826740996</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.343332515287667</v>
+      </c>
+      <c r="J6" t="n">
+        <v>232</v>
+      </c>
+      <c r="K6" t="n">
+        <v>232</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>variable_regime_public</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>adequate</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAIR_DO12</t>
+          <t>DO-R3.0-Q_var</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Q_trend</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>risk_trend</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.7739428300857477</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.326905659409042</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>risk_var</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>1.920042751364567</v>
+        <v>0.3567562499712439</v>
       </c>
       <c r="G7" t="n">
-        <v>2.799466450161726</v>
+        <v>0.6937147422896177</v>
       </c>
       <c r="H7" t="n">
-        <v>4231</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.9209632016677489</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.013938550249727</v>
+      </c>
+      <c r="J7" t="n">
+        <v>232</v>
+      </c>
+      <c r="K7" t="n">
+        <v>232</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>variable_regime_public</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>adequate</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAIR_DO12</t>
+          <t>DO-R1.0-Q_dist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Q_var</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>risk_var</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.1789331730710301</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.3397137809689147</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>risk_dist</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>0.6553035951870532</v>
+        <v>0.2602071569907629</v>
       </c>
       <c r="G8" t="n">
-        <v>1.058127543887885</v>
+        <v>0.3430094821869872</v>
       </c>
       <c r="H8" t="n">
-        <v>4231</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.4491471105559025</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5809742639866085</v>
+      </c>
+      <c r="J8" t="n">
+        <v>215</v>
+      </c>
+      <c r="K8" t="n">
+        <v>215</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>variable_regime_public</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>adequate</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAIR_DO12</t>
+          <t>DO-R1.0-Q_trend</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Q_cp</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>risk_cp</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.2863974007398348</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.4929409516791082</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>risk_trend</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>0.6971522646585302</v>
+        <v>0.7968076656667717</v>
       </c>
       <c r="G9" t="n">
-        <v>0.889835096212876</v>
+        <v>1.33722845008865</v>
       </c>
       <c r="H9" t="n">
-        <v>4231</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>1.70732977276248</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.305485020554439</v>
+      </c>
+      <c r="J9" t="n">
+        <v>215</v>
+      </c>
+      <c r="K9" t="n">
+        <v>215</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>variable_regime_public</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>adequate</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAIR_DO13</t>
+          <t>DO-R1.0-Q_var</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Q_dist</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>risk_dist</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.2638655126913632</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.3863737379062655</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>risk_var</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>0.5265872400622047</v>
+        <v>0.06229309856731934</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7976605333283407</v>
+        <v>0.18557530957591</v>
       </c>
       <c r="H10" t="n">
-        <v>4231</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.3114559616405695</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5056675448111005</v>
+      </c>
+      <c r="J10" t="n">
+        <v>215</v>
+      </c>
+      <c r="K10" t="n">
+        <v>215</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>variable_regime_public</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>adequate</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAIR_DO13</t>
+          <t>DO-R0.0-Q_dist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Q_trend</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>risk_trend</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.8200077742807488</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1.365497009984298</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>risk_dist</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>1.938353246815833</v>
+        <v>0.2056481304026203</v>
       </c>
       <c r="G11" t="n">
-        <v>2.587563377748598</v>
+        <v>0.2880069829208482</v>
       </c>
       <c r="H11" t="n">
-        <v>4231</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.3746800067351109</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.5532088247856335</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1252</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1252</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>variable_regime_public</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>adequate</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PAIR_DO13</t>
+          <t>DO-R0.0-Q_trend</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Q_var</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>risk_var</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.2205914808731309</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.39511752162022</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>risk_trend</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>0.5889274839530404</v>
+        <v>0.6843940821423393</v>
       </c>
       <c r="G12" t="n">
-        <v>0.814928748117399</v>
+        <v>1.130216559955855</v>
       </c>
       <c r="H12" t="n">
-        <v>4231</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>1.60885811913072</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.109438278463575</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1252</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1252</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>variable_regime_public</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>adequate</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAIR_DO13</t>
+          <t>DO-R0.0-Q_var</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Q_cp</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>risk_cp</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.2930209063520663</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.5224878820550358</v>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>risk_var</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>0.7167930556406502</v>
+        <v>0.1199037400013597</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9017257115322305</v>
+        <v>0.2153781296281145</v>
       </c>
       <c r="H13" t="n">
-        <v>4231</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.3392046875039316</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4975192441711737</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1252</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1252</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>variable_regime_public</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>adequate</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PAIR_DO14</t>
+          <t>DO-Rnan-Q_dist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Q_dist</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>risk_dist</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>0.4104207127527817</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.5333442544727925</v>
-      </c>
       <c r="F14" t="n">
-        <v>0.6886200268454218</v>
+        <v>0.2322270751764441</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8931540409202361</v>
+        <v>0.3312833523356252</v>
       </c>
       <c r="H14" t="n">
-        <v>1117</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.4758580166098899</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6925520595588971</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2043</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PAIR_DO14</t>
+          <t>DO-Rnan-Q_trend</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Q_trend</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>risk_trend</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>0.691230622484867</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.279359060982183</v>
-      </c>
       <c r="F15" t="n">
-        <v>1.883051058403393</v>
+        <v>0.6951209192544238</v>
       </c>
       <c r="G15" t="n">
-        <v>2.640581242715434</v>
+        <v>1.16286004399905</v>
       </c>
       <c r="H15" t="n">
-        <v>1117</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>1.630853768283959</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.23586281883549</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2043</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PAIR_DO14</t>
+          <t>DO-Rnan-Q_var</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Q_var</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>risk_var</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>0.07328094167778931</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.4960743183900744</v>
-      </c>
       <c r="F16" t="n">
-        <v>0.6594736089386565</v>
+        <v>0.1346207855701711</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7855684988557556</v>
+        <v>0.2541427629945529</v>
       </c>
       <c r="H16" t="n">
-        <v>1117</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.4309734915149224</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7475680131645497</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2043</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PAIR_DO14</t>
+          <t>ORP-R2.0-Q_dist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Q_cp</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>risk_cp</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0.2758975725469267</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.5268423043741846</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>risk_dist</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>0.7214841045092373</v>
+        <v>0.3092909955571783</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9435181807889697</v>
+        <v>0.4132136963324524</v>
       </c>
       <c r="H17" t="n">
-        <v>1117</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.5461572430350132</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8834475827352465</v>
+      </c>
+      <c r="J17" t="n">
+        <v>97</v>
+      </c>
+      <c r="K17" t="n">
+        <v>31</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PAIR_ORP11</t>
+          <t>ORP-R2.0-Q_trend</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Q_dist</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>risk_dist</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.3108279328103794</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.4377532975758082</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>risk_trend</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>0.557703472424725</v>
+        <v>0.8503428888397229</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7560835792847054</v>
+        <v>1.563209218638637</v>
       </c>
       <c r="H18" t="n">
-        <v>4049</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>2.176134225390203</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.102856757255951</v>
+      </c>
+      <c r="J18" t="n">
+        <v>97</v>
+      </c>
+      <c r="K18" t="n">
+        <v>31</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PAIR_ORP11</t>
+          <t>ORP-R2.0-Q_var</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Q_trend</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>risk_trend</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.7088196544494438</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1.281506894611673</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>risk_var</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>1.869152122728785</v>
+        <v>0.1934938630320244</v>
       </c>
       <c r="G19" t="n">
-        <v>2.603042412751982</v>
+        <v>0.3640980359253088</v>
       </c>
       <c r="H19" t="n">
-        <v>4049</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.513073703715715</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.5927602074783934</v>
+      </c>
+      <c r="J19" t="n">
+        <v>97</v>
+      </c>
+      <c r="K19" t="n">
+        <v>31</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PAIR_ORP11</t>
+          <t>ORP-R3.0-Q_dist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Q_var</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>risk_var</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.1875477832516124</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.3797491044308503</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>risk_dist</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>0.5935702854441696</v>
+        <v>0.3092909955571783</v>
       </c>
       <c r="G20" t="n">
-        <v>0.884715787609748</v>
+        <v>0.4132136963324524</v>
       </c>
       <c r="H20" t="n">
-        <v>4049</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.5461572430350132</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8834475827352465</v>
+      </c>
+      <c r="J20" t="n">
+        <v>97</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PAIR_ORP11</t>
+          <t>ORP-R3.0-Q_trend</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Q_cp</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>risk_cp</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.2535575618625838</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.4637588178256948</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>risk_trend</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>0.6667548225267789</v>
+        <v>0.8503428888397229</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8702313028643115</v>
+        <v>1.563209218638637</v>
       </c>
       <c r="H21" t="n">
-        <v>4049</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>2.176134225390203</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.102856757255951</v>
+      </c>
+      <c r="J21" t="n">
+        <v>97</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PAIR_ORP12</t>
+          <t>ORP-R3.0-Q_var</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Q_dist</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>risk_dist</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0.4167953592887904</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.5374335905944247</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>risk_var</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>0.6346320480572291</v>
+        <v>0.1934938630320244</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7606470033352227</v>
+        <v>0.3640980359253088</v>
       </c>
       <c r="H22" t="n">
-        <v>4040</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.513073703715715</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.5927602074783934</v>
+      </c>
+      <c r="J22" t="n">
+        <v>97</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PAIR_ORP12</t>
+          <t>ORP-R1.0-Q_dist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Q_trend</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>risk_trend</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.8622391492480632</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1.44574485754534</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>risk_dist</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>2.171575118334679</v>
+        <v>0.3092909955571783</v>
       </c>
       <c r="G23" t="n">
-        <v>2.958253145903726</v>
+        <v>0.4132136963324524</v>
       </c>
       <c r="H23" t="n">
-        <v>4040</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.5461572430350132</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8834475827352465</v>
+      </c>
+      <c r="J23" t="n">
+        <v>97</v>
+      </c>
+      <c r="K23" t="n">
+        <v>29</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PAIR_ORP12</t>
+          <t>ORP-R1.0-Q_trend</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Q_var</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>risk_var</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0.3998651564877391</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.606952585313476</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>risk_trend</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>0.8762641226009493</v>
+        <v>0.8503428888397229</v>
       </c>
       <c r="G24" t="n">
-        <v>1.455335227426142</v>
+        <v>1.563209218638637</v>
       </c>
       <c r="H24" t="n">
-        <v>4040</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>2.176134225390203</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.102856757255951</v>
+      </c>
+      <c r="J24" t="n">
+        <v>97</v>
+      </c>
+      <c r="K24" t="n">
+        <v>29</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PAIR_ORP12</t>
+          <t>ORP-R1.0-Q_var</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Q_cp</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>risk_cp</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0.2613265590939134</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.4704723669851247</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>risk_var</t>
+        </is>
       </c>
       <c r="F25" t="n">
-        <v>0.6858601078900259</v>
+        <v>0.1934938630320244</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8776015037159002</v>
+        <v>0.3640980359253088</v>
       </c>
       <c r="H25" t="n">
-        <v>4040</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.513073703715715</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.5927602074783934</v>
+      </c>
+      <c r="J25" t="n">
+        <v>97</v>
+      </c>
+      <c r="K25" t="n">
+        <v>29</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PAIR_ORP13</t>
+          <t>ORP-R0.0-Q_dist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>Q_dist</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>risk_dist</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>0.4743393358706406</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.6602199142261888</v>
-      </c>
       <c r="F26" t="n">
-        <v>0.8889076177118262</v>
+        <v>0.3092909955571783</v>
       </c>
       <c r="G26" t="n">
-        <v>1.314098522386624</v>
+        <v>0.4132136963324524</v>
       </c>
       <c r="H26" t="n">
-        <v>3467</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.5461572430350132</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8834475827352465</v>
+      </c>
+      <c r="J26" t="n">
+        <v>97</v>
+      </c>
+      <c r="K26" t="n">
+        <v>17</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PAIR_ORP13</t>
+          <t>ORP-R0.0-Q_trend</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>Q_trend</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>risk_trend</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>1.479227130856674</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2.262116166160102</v>
-      </c>
       <c r="F27" t="n">
-        <v>2.913133156414182</v>
+        <v>0.8503428888397229</v>
       </c>
       <c r="G27" t="n">
-        <v>3.554792681521135</v>
+        <v>1.563209218638637</v>
       </c>
       <c r="H27" t="n">
-        <v>3467</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>2.176134225390203</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.102856757255951</v>
+      </c>
+      <c r="J27" t="n">
+        <v>97</v>
+      </c>
+      <c r="K27" t="n">
+        <v>17</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PAIR_ORP13</t>
+          <t>ORP-R0.0-Q_var</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>Q_var</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>risk_var</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>0.4980769179073794</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.8417916204542714</v>
-      </c>
       <c r="F28" t="n">
-        <v>1.263339811748221</v>
+        <v>0.1934938630320244</v>
       </c>
       <c r="G28" t="n">
-        <v>1.694293686414343</v>
+        <v>0.3640980359253088</v>
       </c>
       <c r="H28" t="n">
-        <v>3467</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.513073703715715</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.5927602074783934</v>
+      </c>
+      <c r="J28" t="n">
+        <v>97</v>
+      </c>
+      <c r="K28" t="n">
+        <v>17</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PAIR_ORP13</t>
+          <t>ORP-Rnan-Q_dist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Q_cp</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>risk_cp</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0.3669861940117947</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.6173545453594089</v>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Q_dist</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>risk_dist</t>
+        </is>
       </c>
       <c r="F29" t="n">
-        <v>0.8307769946139435</v>
+        <v>0.3092909955571783</v>
       </c>
       <c r="G29" t="n">
-        <v>0.974361310550628</v>
+        <v>0.4132136963324524</v>
       </c>
       <c r="H29" t="n">
-        <v>3467</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>first70pct_D2_nonveto</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>46049.45833333334</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>pair_specific_quantile</t>
+        <v>0.5461572430350132</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8834475827352465</v>
+      </c>
+      <c r="J29" t="n">
+        <v>97</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ORP-Rnan-Q_trend</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Q_trend</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>risk_trend</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.8503428888397229</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.563209218638637</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.176134225390203</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.102856757255951</v>
+      </c>
+      <c r="J30" t="n">
+        <v>97</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ORP-Rnan-Q_var</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Q_var</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>risk_var</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0.1934938630320244</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3640980359253088</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.513073703715715</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.5927602074783934</v>
+      </c>
+      <c r="J31" t="n">
+        <v>97</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>variable_public_fallback</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>limited_regime_support</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>v1.2_high_quality_public_D7pending</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>public_quantile_by_variable_and_regime</t>
         </is>
       </c>
     </row>
@@ -1885,7 +2519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1896,19 +2530,39 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>calibration_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>run_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>D7_status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d6-v1.3-independent-20260713</t>
+          <t>d6-v1.4-restored-v12-20260714</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D6V13_20260713_103039</t>
+          <t>D6CAL-V14-20f697901061</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>D6V14_20260714_024929</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pending_not_available</t>
         </is>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D6 Parallel-redundancy Temporal Consistency/outputs/data/D6_mapping_params.xlsx
+++ b/Project 1 Data Quality Assessment/D6 Parallel-redundancy Temporal Consistency/outputs/data/D6_mapping_params.xlsx
@@ -533,22 +533,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2504154359800578</v>
+        <v>0.2093736003153026</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3338236766084912</v>
+        <v>0.2960692866833398</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4280023665920573</v>
+        <v>0.3844410152491148</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6602663723924389</v>
+        <v>0.5395167224315538</v>
       </c>
       <c r="J2" t="n">
-        <v>344</v>
+        <v>1006</v>
       </c>
       <c r="K2" t="n">
-        <v>344</v>
+        <v>1006</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -596,22 +596,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.5367493751120398</v>
+        <v>0.5889092866829994</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9088822902507345</v>
+        <v>1.014632664163266</v>
       </c>
       <c r="H3" t="n">
-        <v>1.262118579655626</v>
+        <v>1.420263105374823</v>
       </c>
       <c r="I3" t="n">
-        <v>1.606347933993035</v>
+        <v>1.774066437813467</v>
       </c>
       <c r="J3" t="n">
-        <v>344</v>
+        <v>1006</v>
       </c>
       <c r="K3" t="n">
-        <v>344</v>
+        <v>1006</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.1549026540026797</v>
+        <v>0.1153096528899995</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2643708304244196</v>
+        <v>0.1930425226579245</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4083907052416982</v>
+        <v>0.319835192540662</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5931410151814244</v>
+        <v>0.5071769375847248</v>
       </c>
       <c r="J4" t="n">
-        <v>344</v>
+        <v>1006</v>
       </c>
       <c r="K4" t="n">
-        <v>344</v>
+        <v>1006</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.4576931600782945</v>
+        <v>0.4397556826670835</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5935612000600703</v>
+        <v>0.574299847795482</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7789426749644821</v>
+        <v>0.723575250093613</v>
       </c>
       <c r="I5" t="n">
-        <v>1.073665920603763</v>
+        <v>0.9456319560386566</v>
       </c>
       <c r="J5" t="n">
-        <v>232</v>
+        <v>448</v>
       </c>
       <c r="K5" t="n">
-        <v>232</v>
+        <v>448</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -785,22 +785,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.9738773107279557</v>
+        <v>0.9185194966211299</v>
       </c>
       <c r="G6" t="n">
-        <v>1.606268008652675</v>
+        <v>1.479754354230112</v>
       </c>
       <c r="H6" t="n">
-        <v>2.234776826740996</v>
+        <v>2.196571702945604</v>
       </c>
       <c r="I6" t="n">
-        <v>3.343332515287667</v>
+        <v>3.105435749385174</v>
       </c>
       <c r="J6" t="n">
-        <v>232</v>
+        <v>448</v>
       </c>
       <c r="K6" t="n">
-        <v>232</v>
+        <v>448</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.3567562499712439</v>
+        <v>0.3527811835684971</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6937147422896177</v>
+        <v>0.5862052203838896</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9209632016677489</v>
+        <v>0.8982877350723503</v>
       </c>
       <c r="I7" t="n">
-        <v>1.013938550249727</v>
+        <v>1.191242734737836</v>
       </c>
       <c r="J7" t="n">
-        <v>232</v>
+        <v>448</v>
       </c>
       <c r="K7" t="n">
-        <v>232</v>
+        <v>448</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -911,22 +911,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.2602071569907629</v>
+        <v>0.2500864488843678</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3430094821869872</v>
+        <v>0.3340434948569844</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4491471105559025</v>
+        <v>0.4437838047034954</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5809742639866085</v>
+        <v>0.5741685290788018</v>
       </c>
       <c r="J8" t="n">
-        <v>215</v>
+        <v>725</v>
       </c>
       <c r="K8" t="n">
-        <v>215</v>
+        <v>725</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -974,22 +974,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.7968076656667717</v>
+        <v>0.7058463993473845</v>
       </c>
       <c r="G9" t="n">
-        <v>1.33722845008865</v>
+        <v>1.213867513683193</v>
       </c>
       <c r="H9" t="n">
-        <v>1.70732977276248</v>
+        <v>1.621455888661407</v>
       </c>
       <c r="I9" t="n">
-        <v>2.305485020554439</v>
+        <v>2.289183017840378</v>
       </c>
       <c r="J9" t="n">
-        <v>215</v>
+        <v>725</v>
       </c>
       <c r="K9" t="n">
-        <v>215</v>
+        <v>725</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1037,22 +1037,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.06229309856731934</v>
+        <v>0.1270057521641811</v>
       </c>
       <c r="G10" t="n">
-        <v>0.18557530957591</v>
+        <v>0.2587271071617021</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3114559616405695</v>
+        <v>0.3835505137060765</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5056675448111005</v>
+        <v>0.542446248960522</v>
       </c>
       <c r="J10" t="n">
-        <v>215</v>
+        <v>725</v>
       </c>
       <c r="K10" t="n">
-        <v>215</v>
+        <v>725</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1100,22 +1100,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.2056481304026203</v>
+        <v>0.2164426108373096</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2880069829208482</v>
+        <v>0.2993636291754685</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3746800067351109</v>
+        <v>0.3923315011530756</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5532088247856335</v>
+        <v>0.5588366191246812</v>
       </c>
       <c r="J11" t="n">
-        <v>1252</v>
+        <v>2305</v>
       </c>
       <c r="K11" t="n">
-        <v>1252</v>
+        <v>2305</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1163,22 +1163,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.6843940821423393</v>
+        <v>0.6812971302486175</v>
       </c>
       <c r="G12" t="n">
-        <v>1.130216559955855</v>
+        <v>1.117617824642894</v>
       </c>
       <c r="H12" t="n">
-        <v>1.60885811913072</v>
+        <v>1.579214114205228</v>
       </c>
       <c r="I12" t="n">
-        <v>2.109438278463575</v>
+        <v>2.123411843849475</v>
       </c>
       <c r="J12" t="n">
-        <v>1252</v>
+        <v>2305</v>
       </c>
       <c r="K12" t="n">
-        <v>1252</v>
+        <v>2305</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1226,22 +1226,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.1199037400013597</v>
+        <v>0.140986388375354</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2153781296281145</v>
+        <v>0.2512426248978984</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3392046875039316</v>
+        <v>0.4033639693276171</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4975192441711737</v>
+        <v>0.5492681670699867</v>
       </c>
       <c r="J13" t="n">
-        <v>1252</v>
+        <v>2305</v>
       </c>
       <c r="K13" t="n">
-        <v>1252</v>
+        <v>2305</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.2322270751764441</v>
+        <v>0.2320591894782433</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3312833523356252</v>
+        <v>0.3297199021099788</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4758580166098899</v>
+        <v>0.4551027854189134</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6925520595588971</v>
+        <v>0.6680352863447503</v>
       </c>
       <c r="J14" t="n">
-        <v>2043</v>
+        <v>4484</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.6951209192544238</v>
+        <v>0.6823701362509162</v>
       </c>
       <c r="G15" t="n">
-        <v>1.16286004399905</v>
+        <v>1.138343937097956</v>
       </c>
       <c r="H15" t="n">
-        <v>1.630853768283959</v>
+        <v>1.597974409376788</v>
       </c>
       <c r="I15" t="n">
-        <v>2.23586281883549</v>
+        <v>2.226184984660133</v>
       </c>
       <c r="J15" t="n">
-        <v>2043</v>
+        <v>4484</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1409,19 +1409,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.1346207855701711</v>
+        <v>0.1416148375179612</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2541427629945529</v>
+        <v>0.2656187444524272</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4309734915149224</v>
+        <v>0.4320210169941225</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7475680131645497</v>
+        <v>0.7206031351247632</v>
       </c>
       <c r="J16" t="n">
-        <v>2043</v>
+        <v>4484</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1472,31 +1472,31 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.3092909955571783</v>
+        <v>0.2977514937310022</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4132136963324524</v>
+        <v>0.437097965305368</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5461572430350132</v>
+        <v>0.4854898457259077</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8834475827352465</v>
+        <v>0.8105610286963836</v>
       </c>
       <c r="J17" t="n">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="K17" t="n">
-        <v>31</v>
+        <v>161</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>variable_public_fallback</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1535,31 +1535,31 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.8503428888397229</v>
+        <v>0.6224300957290685</v>
       </c>
       <c r="G18" t="n">
-        <v>1.563209218638637</v>
+        <v>1.324562185933621</v>
       </c>
       <c r="H18" t="n">
-        <v>2.176134225390203</v>
+        <v>1.742226578181193</v>
       </c>
       <c r="I18" t="n">
-        <v>3.102856757255951</v>
+        <v>2.359673958550975</v>
       </c>
       <c r="J18" t="n">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="K18" t="n">
-        <v>31</v>
+        <v>161</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>variable_public_fallback</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1598,31 +1598,31 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.1934938630320244</v>
+        <v>0.1204923425871819</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3640980359253088</v>
+        <v>0.3943141017559065</v>
       </c>
       <c r="H19" t="n">
-        <v>0.513073703715715</v>
+        <v>0.5471953783467834</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5927602074783934</v>
+        <v>0.7150551816212879</v>
       </c>
       <c r="J19" t="n">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="K19" t="n">
-        <v>31</v>
+        <v>161</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>variable_public_fallback</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1661,22 +1661,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.3092909955571783</v>
+        <v>0.323782007519899</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4132136963324524</v>
+        <v>0.4230270715287825</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5461572430350132</v>
+        <v>0.560560587059901</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8834475827352465</v>
+        <v>0.7858323996329015</v>
       </c>
       <c r="J20" t="n">
-        <v>97</v>
+        <v>402</v>
       </c>
       <c r="K20" t="n">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1724,22 +1724,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.8503428888397229</v>
+        <v>0.7844172091575227</v>
       </c>
       <c r="G21" t="n">
-        <v>1.563209218638637</v>
+        <v>1.509869144964552</v>
       </c>
       <c r="H21" t="n">
-        <v>2.176134225390203</v>
+        <v>2.236063926398112</v>
       </c>
       <c r="I21" t="n">
-        <v>3.102856757255951</v>
+        <v>2.98662278132344</v>
       </c>
       <c r="J21" t="n">
-        <v>97</v>
+        <v>402</v>
       </c>
       <c r="K21" t="n">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1787,22 +1787,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.1934938630320244</v>
+        <v>0.2547107749843295</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3640980359253088</v>
+        <v>0.4099539242487948</v>
       </c>
       <c r="H22" t="n">
-        <v>0.513073703715715</v>
+        <v>0.5778745687706941</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5927602074783934</v>
+        <v>0.6885985173894739</v>
       </c>
       <c r="J22" t="n">
-        <v>97</v>
+        <v>402</v>
       </c>
       <c r="K22" t="n">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1850,22 +1850,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.3092909955571783</v>
+        <v>0.323782007519899</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4132136963324524</v>
+        <v>0.4230270715287825</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5461572430350132</v>
+        <v>0.560560587059901</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8834475827352465</v>
+        <v>0.7858323996329015</v>
       </c>
       <c r="J23" t="n">
-        <v>97</v>
+        <v>402</v>
       </c>
       <c r="K23" t="n">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1913,22 +1913,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.8503428888397229</v>
+        <v>0.7844172091575227</v>
       </c>
       <c r="G24" t="n">
-        <v>1.563209218638637</v>
+        <v>1.509869144964552</v>
       </c>
       <c r="H24" t="n">
-        <v>2.176134225390203</v>
+        <v>2.236063926398112</v>
       </c>
       <c r="I24" t="n">
-        <v>3.102856757255951</v>
+        <v>2.98662278132344</v>
       </c>
       <c r="J24" t="n">
-        <v>97</v>
+        <v>402</v>
       </c>
       <c r="K24" t="n">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1976,22 +1976,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.1934938630320244</v>
+        <v>0.2547107749843295</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3640980359253088</v>
+        <v>0.4099539242487948</v>
       </c>
       <c r="H25" t="n">
-        <v>0.513073703715715</v>
+        <v>0.5778745687706941</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5927602074783934</v>
+        <v>0.6885985173894739</v>
       </c>
       <c r="J25" t="n">
-        <v>97</v>
+        <v>402</v>
       </c>
       <c r="K25" t="n">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2039,22 +2039,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.3092909955571783</v>
+        <v>0.323782007519899</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4132136963324524</v>
+        <v>0.4230270715287825</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5461572430350132</v>
+        <v>0.560560587059901</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8834475827352465</v>
+        <v>0.7858323996329015</v>
       </c>
       <c r="J26" t="n">
-        <v>97</v>
+        <v>402</v>
       </c>
       <c r="K26" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2102,22 +2102,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.8503428888397229</v>
+        <v>0.7844172091575227</v>
       </c>
       <c r="G27" t="n">
-        <v>1.563209218638637</v>
+        <v>1.509869144964552</v>
       </c>
       <c r="H27" t="n">
-        <v>2.176134225390203</v>
+        <v>2.236063926398112</v>
       </c>
       <c r="I27" t="n">
-        <v>3.102856757255951</v>
+        <v>2.98662278132344</v>
       </c>
       <c r="J27" t="n">
-        <v>97</v>
+        <v>402</v>
       </c>
       <c r="K27" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2165,22 +2165,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.1934938630320244</v>
+        <v>0.2547107749843295</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3640980359253088</v>
+        <v>0.4099539242487948</v>
       </c>
       <c r="H28" t="n">
-        <v>0.513073703715715</v>
+        <v>0.5778745687706941</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5927602074783934</v>
+        <v>0.6885985173894739</v>
       </c>
       <c r="J28" t="n">
-        <v>97</v>
+        <v>402</v>
       </c>
       <c r="K28" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2226,19 +2226,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.3092909955571783</v>
+        <v>0.323782007519899</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4132136963324524</v>
+        <v>0.4230270715287825</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5461572430350132</v>
+        <v>0.560560587059901</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8834475827352465</v>
+        <v>0.7858323996329015</v>
       </c>
       <c r="J29" t="n">
-        <v>97</v>
+        <v>402</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2287,19 +2287,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.8503428888397229</v>
+        <v>0.7844172091575227</v>
       </c>
       <c r="G30" t="n">
-        <v>1.563209218638637</v>
+        <v>1.509869144964552</v>
       </c>
       <c r="H30" t="n">
-        <v>2.176134225390203</v>
+        <v>2.236063926398112</v>
       </c>
       <c r="I30" t="n">
-        <v>3.102856757255951</v>
+        <v>2.98662278132344</v>
       </c>
       <c r="J30" t="n">
-        <v>97</v>
+        <v>402</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2348,19 +2348,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.1934938630320244</v>
+        <v>0.2547107749843295</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3640980359253088</v>
+        <v>0.4099539242487948</v>
       </c>
       <c r="H31" t="n">
-        <v>0.513073703715715</v>
+        <v>0.5778745687706941</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5927602074783934</v>
+        <v>0.6885985173894739</v>
       </c>
       <c r="J31" t="n">
-        <v>97</v>
+        <v>402</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D6CAL-V14-20f697901061</t>
+          <t>D6CAL-V14-d21144ef1b41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>D6V14_20260714_024929</t>
+          <t>D6V14_20260722_021007</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D6 Parallel-redundancy Temporal Consistency/outputs/data/D6_mapping_params.xlsx
+++ b/Project 1 Data Quality Assessment/D6 Parallel-redundancy Temporal Consistency/outputs/data/D6_mapping_params.xlsx
@@ -533,22 +533,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2093736003153026</v>
+        <v>0.2181624540335634</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2960692866833398</v>
+        <v>0.3133887134903199</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3844410152491148</v>
+        <v>0.4291660232066167</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5395167224315538</v>
+        <v>0.7052089229378596</v>
       </c>
       <c r="J2" t="n">
-        <v>1006</v>
+        <v>1060</v>
       </c>
       <c r="K2" t="n">
-        <v>1006</v>
+        <v>1060</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -596,22 +596,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.5889092866829994</v>
+        <v>0.6089235361301848</v>
       </c>
       <c r="G3" t="n">
-        <v>1.014632664163266</v>
+        <v>1.033520067229793</v>
       </c>
       <c r="H3" t="n">
-        <v>1.420263105374823</v>
+        <v>1.444743793346957</v>
       </c>
       <c r="I3" t="n">
-        <v>1.774066437813467</v>
+        <v>1.920689454334735</v>
       </c>
       <c r="J3" t="n">
-        <v>1006</v>
+        <v>1060</v>
       </c>
       <c r="K3" t="n">
-        <v>1006</v>
+        <v>1060</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.1153096528899995</v>
+        <v>0.1181693395333395</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1930425226579245</v>
+        <v>0.2044106032792038</v>
       </c>
       <c r="H4" t="n">
-        <v>0.319835192540662</v>
+        <v>0.3596491722370428</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5071769375847248</v>
+        <v>0.7546981250170745</v>
       </c>
       <c r="J4" t="n">
-        <v>1006</v>
+        <v>1060</v>
       </c>
       <c r="K4" t="n">
-        <v>1006</v>
+        <v>1060</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.4397556826670835</v>
+        <v>0.4755043423023069</v>
       </c>
       <c r="G5" t="n">
-        <v>0.574299847795482</v>
+        <v>0.6924955311560432</v>
       </c>
       <c r="H5" t="n">
-        <v>0.723575250093613</v>
+        <v>0.8885957586485553</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9456319560386566</v>
+        <v>1.122775053764726</v>
       </c>
       <c r="J5" t="n">
-        <v>448</v>
+        <v>524</v>
       </c>
       <c r="K5" t="n">
-        <v>448</v>
+        <v>524</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -785,22 +785,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.9185194966211299</v>
+        <v>0.9483776611868711</v>
       </c>
       <c r="G6" t="n">
-        <v>1.479754354230112</v>
+        <v>1.575393096538618</v>
       </c>
       <c r="H6" t="n">
-        <v>2.196571702945604</v>
+        <v>2.281514551029057</v>
       </c>
       <c r="I6" t="n">
-        <v>3.105435749385174</v>
+        <v>3.295138565271943</v>
       </c>
       <c r="J6" t="n">
-        <v>448</v>
+        <v>524</v>
       </c>
       <c r="K6" t="n">
-        <v>448</v>
+        <v>524</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.3527811835684971</v>
+        <v>0.4236001924571131</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5862052203838896</v>
+        <v>0.7655761868625628</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8982877350723503</v>
+        <v>0.9589430132834768</v>
       </c>
       <c r="I7" t="n">
-        <v>1.191242734737836</v>
+        <v>1.191281151644254</v>
       </c>
       <c r="J7" t="n">
-        <v>448</v>
+        <v>524</v>
       </c>
       <c r="K7" t="n">
-        <v>448</v>
+        <v>524</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -911,22 +911,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.2500864488843678</v>
+        <v>0.2525203916251205</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3340434948569844</v>
+        <v>0.3366883036277407</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4437838047034954</v>
+        <v>0.4478292672257014</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5741685290788018</v>
+        <v>0.6098356108735087</v>
       </c>
       <c r="J8" t="n">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="K8" t="n">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -974,22 +974,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.7058463993473845</v>
+        <v>0.7007107543841994</v>
       </c>
       <c r="G9" t="n">
-        <v>1.213867513683193</v>
+        <v>1.206309098179878</v>
       </c>
       <c r="H9" t="n">
-        <v>1.621455888661407</v>
+        <v>1.621040132442261</v>
       </c>
       <c r="I9" t="n">
-        <v>2.289183017840378</v>
+        <v>2.283836091422137</v>
       </c>
       <c r="J9" t="n">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="K9" t="n">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1037,22 +1037,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.1270057521641811</v>
+        <v>0.1247248170852662</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2587271071617021</v>
+        <v>0.2581888438171047</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3835505137060765</v>
+        <v>0.3843851985421037</v>
       </c>
       <c r="I10" t="n">
-        <v>0.542446248960522</v>
+        <v>0.5726308411157923</v>
       </c>
       <c r="J10" t="n">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="K10" t="n">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1100,22 +1100,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.2164426108373096</v>
+        <v>0.2167665307866929</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2993636291754685</v>
+        <v>0.300769119446163</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3923315011530756</v>
+        <v>0.3932498291761582</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5588366191246812</v>
+        <v>0.561422390573258</v>
       </c>
       <c r="J11" t="n">
-        <v>2305</v>
+        <v>2316</v>
       </c>
       <c r="K11" t="n">
-        <v>2305</v>
+        <v>2316</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1163,22 +1163,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.6812971302486175</v>
+        <v>0.6816065607760247</v>
       </c>
       <c r="G12" t="n">
-        <v>1.117617824642894</v>
+        <v>1.118979995521794</v>
       </c>
       <c r="H12" t="n">
-        <v>1.579214114205228</v>
+        <v>1.583698469451417</v>
       </c>
       <c r="I12" t="n">
-        <v>2.123411843849475</v>
+        <v>2.130126683566745</v>
       </c>
       <c r="J12" t="n">
-        <v>2305</v>
+        <v>2316</v>
       </c>
       <c r="K12" t="n">
-        <v>2305</v>
+        <v>2316</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1226,22 +1226,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.140986388375354</v>
+        <v>0.1408893020387061</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2512426248978984</v>
+        <v>0.2523063720237416</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4033639693276171</v>
+        <v>0.403795376447266</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5492681670699867</v>
+        <v>0.5502059101881052</v>
       </c>
       <c r="J13" t="n">
-        <v>2305</v>
+        <v>2316</v>
       </c>
       <c r="K13" t="n">
-        <v>2305</v>
+        <v>2316</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.2320591894782433</v>
+        <v>0.2379118056706658</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3297199021099788</v>
+        <v>0.3413532390203972</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4551027854189134</v>
+        <v>0.4974344750457913</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6680352863447503</v>
+        <v>0.778035562034328</v>
       </c>
       <c r="J14" t="n">
-        <v>4484</v>
+        <v>4646</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.6823701362509162</v>
+        <v>0.6881375672118664</v>
       </c>
       <c r="G15" t="n">
-        <v>1.138343937097956</v>
+        <v>1.15244555063635</v>
       </c>
       <c r="H15" t="n">
-        <v>1.597974409376788</v>
+        <v>1.617401398170177</v>
       </c>
       <c r="I15" t="n">
-        <v>2.226184984660133</v>
+        <v>2.315373671580646</v>
       </c>
       <c r="J15" t="n">
-        <v>4484</v>
+        <v>4646</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1409,19 +1409,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.1416148375179612</v>
+        <v>0.1440469446085341</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2656187444524272</v>
+        <v>0.2784318203557657</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4320210169941225</v>
+        <v>0.4750291623422657</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7206031351247632</v>
+        <v>0.8501314147501072</v>
       </c>
       <c r="J16" t="n">
-        <v>4484</v>
+        <v>4646</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1472,22 +1472,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.2977514937310022</v>
+        <v>0.2759997578094889</v>
       </c>
       <c r="G17" t="n">
-        <v>0.437097965305368</v>
+        <v>0.4197024771651728</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4854898457259077</v>
+        <v>0.479798045086721</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8105610286963836</v>
+        <v>0.5939238998259706</v>
       </c>
       <c r="J17" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="K17" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1535,22 +1535,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.6224300957290685</v>
+        <v>0.6217121253038793</v>
       </c>
       <c r="G18" t="n">
-        <v>1.324562185933621</v>
+        <v>1.142374564881111</v>
       </c>
       <c r="H18" t="n">
-        <v>1.742226578181193</v>
+        <v>1.728859220681275</v>
       </c>
       <c r="I18" t="n">
-        <v>2.359673958550975</v>
+        <v>2.256419477775076</v>
       </c>
       <c r="J18" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="K18" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1598,22 +1598,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.1204923425871819</v>
+        <v>0.04577498858176644</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3943141017559065</v>
+        <v>0.3851290392046844</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5471953783467834</v>
+        <v>0.5449238159171348</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7150551816212879</v>
+        <v>0.7199690094883338</v>
       </c>
       <c r="J19" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="K19" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1661,22 +1661,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.323782007519899</v>
+        <v>0.3108362828864705</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4230270715287825</v>
+        <v>0.414384657314653</v>
       </c>
       <c r="H20" t="n">
-        <v>0.560560587059901</v>
+        <v>0.5185623668249223</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7858323996329015</v>
+        <v>0.7177497060330877</v>
       </c>
       <c r="J20" t="n">
-        <v>402</v>
+        <v>312</v>
       </c>
       <c r="K20" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1724,22 +1724,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.7844172091575227</v>
+        <v>0.7177958739646288</v>
       </c>
       <c r="G21" t="n">
-        <v>1.509869144964552</v>
+        <v>1.365266655703362</v>
       </c>
       <c r="H21" t="n">
-        <v>2.236063926398112</v>
+        <v>1.883917248843737</v>
       </c>
       <c r="I21" t="n">
-        <v>2.98662278132344</v>
+        <v>2.658382603775709</v>
       </c>
       <c r="J21" t="n">
-        <v>402</v>
+        <v>312</v>
       </c>
       <c r="K21" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1787,22 +1787,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.2547107749843295</v>
+        <v>0.2115030955240084</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4099539242487948</v>
+        <v>0.3986814168111091</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5778745687706941</v>
+        <v>0.5466274877393715</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6885985173894739</v>
+        <v>0.7039127201392978</v>
       </c>
       <c r="J22" t="n">
-        <v>402</v>
+        <v>312</v>
       </c>
       <c r="K22" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1850,22 +1850,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.323782007519899</v>
+        <v>0.3108362828864705</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4230270715287825</v>
+        <v>0.414384657314653</v>
       </c>
       <c r="H23" t="n">
-        <v>0.560560587059901</v>
+        <v>0.5185623668249223</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7858323996329015</v>
+        <v>0.7177497060330877</v>
       </c>
       <c r="J23" t="n">
-        <v>402</v>
+        <v>312</v>
       </c>
       <c r="K23" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1913,22 +1913,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.7844172091575227</v>
+        <v>0.7177958739646288</v>
       </c>
       <c r="G24" t="n">
-        <v>1.509869144964552</v>
+        <v>1.365266655703362</v>
       </c>
       <c r="H24" t="n">
-        <v>2.236063926398112</v>
+        <v>1.883917248843737</v>
       </c>
       <c r="I24" t="n">
-        <v>2.98662278132344</v>
+        <v>2.658382603775709</v>
       </c>
       <c r="J24" t="n">
-        <v>402</v>
+        <v>312</v>
       </c>
       <c r="K24" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1976,22 +1976,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.2547107749843295</v>
+        <v>0.2115030955240084</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4099539242487948</v>
+        <v>0.3986814168111091</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5778745687706941</v>
+        <v>0.5466274877393715</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6885985173894739</v>
+        <v>0.7039127201392978</v>
       </c>
       <c r="J25" t="n">
-        <v>402</v>
+        <v>312</v>
       </c>
       <c r="K25" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2039,22 +2039,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.323782007519899</v>
+        <v>0.3108362828864705</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4230270715287825</v>
+        <v>0.414384657314653</v>
       </c>
       <c r="H26" t="n">
-        <v>0.560560587059901</v>
+        <v>0.5185623668249223</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7858323996329015</v>
+        <v>0.7177497060330877</v>
       </c>
       <c r="J26" t="n">
-        <v>402</v>
+        <v>312</v>
       </c>
       <c r="K26" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2102,22 +2102,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.7844172091575227</v>
+        <v>0.7177958739646288</v>
       </c>
       <c r="G27" t="n">
-        <v>1.509869144964552</v>
+        <v>1.365266655703362</v>
       </c>
       <c r="H27" t="n">
-        <v>2.236063926398112</v>
+        <v>1.883917248843737</v>
       </c>
       <c r="I27" t="n">
-        <v>2.98662278132344</v>
+        <v>2.658382603775709</v>
       </c>
       <c r="J27" t="n">
-        <v>402</v>
+        <v>312</v>
       </c>
       <c r="K27" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2165,22 +2165,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.2547107749843295</v>
+        <v>0.2115030955240084</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4099539242487948</v>
+        <v>0.3986814168111091</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5778745687706941</v>
+        <v>0.5466274877393715</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6885985173894739</v>
+        <v>0.7039127201392978</v>
       </c>
       <c r="J28" t="n">
-        <v>402</v>
+        <v>312</v>
       </c>
       <c r="K28" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2226,19 +2226,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.323782007519899</v>
+        <v>0.3108362828864705</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4230270715287825</v>
+        <v>0.414384657314653</v>
       </c>
       <c r="H29" t="n">
-        <v>0.560560587059901</v>
+        <v>0.5185623668249223</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7858323996329015</v>
+        <v>0.7177497060330877</v>
       </c>
       <c r="J29" t="n">
-        <v>402</v>
+        <v>312</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2287,19 +2287,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.7844172091575227</v>
+        <v>0.7177958739646288</v>
       </c>
       <c r="G30" t="n">
-        <v>1.509869144964552</v>
+        <v>1.365266655703362</v>
       </c>
       <c r="H30" t="n">
-        <v>2.236063926398112</v>
+        <v>1.883917248843737</v>
       </c>
       <c r="I30" t="n">
-        <v>2.98662278132344</v>
+        <v>2.658382603775709</v>
       </c>
       <c r="J30" t="n">
-        <v>402</v>
+        <v>312</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2348,19 +2348,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.2547107749843295</v>
+        <v>0.2115030955240084</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4099539242487948</v>
+        <v>0.3986814168111091</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5778745687706941</v>
+        <v>0.5466274877393715</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6885985173894739</v>
+        <v>0.7039127201392978</v>
       </c>
       <c r="J31" t="n">
-        <v>402</v>
+        <v>312</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D6CAL-V14-d21144ef1b41</t>
+          <t>D6CAL-V14-598338d2c31d</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>D6V14_20260722_021007</t>
+          <t>D6V14_20260722_091650</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
